--- a/diseases/d006/2010-2014.xlsx
+++ b/diseases/d006/2010-2014.xlsx
@@ -987,7 +987,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5112,7 +5112,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -5862,7 +5862,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -6987,7 +6987,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8112,7 +8112,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -8862,7 +8862,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -9612,7 +9612,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -9987,7 +9987,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -10737,7 +10737,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11112,7 +11112,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -11862,7 +11862,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12612,7 +12612,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -12987,7 +12987,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13806,7 +13806,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -14773,7 +14773,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15888,7 +15888,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -16855,7 +16855,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -17822,7 +17822,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -18789,7 +18789,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -19904,7 +19904,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -20871,7 +20871,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -21986,7 +21986,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -22953,7 +22953,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -23920,7 +23920,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -25035,7 +25035,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -26002,7 +26002,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -26969,7 +26969,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -29051,7 +29051,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -30166,7 +30166,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -31133,7 +31133,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -32100,7 +32100,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK186" t="inlineStr">
@@ -33067,7 +33067,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK192" t="inlineStr">
@@ -34182,7 +34182,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -35149,7 +35149,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -36116,7 +36116,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -37231,7 +37231,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
@@ -38198,7 +38198,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -39313,7 +39313,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -40280,7 +40280,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">

--- a/diseases/d006/2010-2014.xlsx
+++ b/diseases/d006/2010-2014.xlsx
@@ -987,7 +987,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5112,7 +5112,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -5862,7 +5862,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -6987,7 +6987,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8112,7 +8112,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -8862,7 +8862,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -9612,7 +9612,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -9987,7 +9987,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -10737,7 +10737,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11112,7 +11112,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -11862,7 +11862,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12612,7 +12612,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -12987,7 +12987,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13806,7 +13806,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -14773,7 +14773,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15888,7 +15888,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -16855,7 +16855,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -17822,7 +17822,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -18789,7 +18789,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -19904,7 +19904,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -20871,7 +20871,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -21986,7 +21986,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -22953,7 +22953,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -23920,7 +23920,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -25035,7 +25035,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -26002,7 +26002,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -26969,7 +26969,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -29051,7 +29051,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -30166,7 +30166,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -31133,7 +31133,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -32100,7 +32100,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK186" t="inlineStr">
@@ -33067,7 +33067,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK192" t="inlineStr">
@@ -34182,7 +34182,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -35149,7 +35149,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -36116,7 +36116,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -37231,7 +37231,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
@@ -38198,7 +38198,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -39313,7 +39313,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -40280,7 +40280,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">

--- a/diseases/d006/2010-2014.xlsx
+++ b/diseases/d006/2010-2014.xlsx
@@ -987,7 +987,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5112,7 +5112,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -5862,7 +5862,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -6987,7 +6987,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8112,7 +8112,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -8862,7 +8862,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -9612,7 +9612,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -9987,7 +9987,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -10737,7 +10737,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11112,7 +11112,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -11862,7 +11862,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12612,7 +12612,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -12987,7 +12987,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13806,7 +13806,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -14773,7 +14773,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15888,7 +15888,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -16855,7 +16855,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -17822,7 +17822,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -18789,7 +18789,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -19904,7 +19904,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -20871,7 +20871,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -21986,7 +21986,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -22953,7 +22953,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -23920,7 +23920,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -25035,7 +25035,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -26002,7 +26002,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -26969,7 +26969,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -29051,7 +29051,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -30166,7 +30166,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -31133,7 +31133,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -32100,7 +32100,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK186" t="inlineStr">
@@ -33067,7 +33067,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK192" t="inlineStr">
@@ -34182,7 +34182,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -35149,7 +35149,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -36116,7 +36116,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -37231,7 +37231,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
@@ -38198,7 +38198,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -39313,7 +39313,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -40280,7 +40280,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">

--- a/diseases/d006/2010-2014.xlsx
+++ b/diseases/d006/2010-2014.xlsx
@@ -987,7 +987,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5112,7 +5112,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -5862,7 +5862,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -6987,7 +6987,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8112,7 +8112,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -8862,7 +8862,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -9612,7 +9612,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -9987,7 +9987,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -10737,7 +10737,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11112,7 +11112,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -11862,7 +11862,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12612,7 +12612,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -12987,7 +12987,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13806,7 +13806,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -14773,7 +14773,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15888,7 +15888,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -16855,7 +16855,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -17822,7 +17822,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -18789,7 +18789,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -19904,7 +19904,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -20871,7 +20871,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -21986,7 +21986,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -22953,7 +22953,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -23920,7 +23920,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -25035,7 +25035,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -26002,7 +26002,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -26969,7 +26969,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -29051,7 +29051,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -30166,7 +30166,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -31133,7 +31133,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -32100,7 +32100,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK186" t="inlineStr">
@@ -33067,7 +33067,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK192" t="inlineStr">
@@ -34182,7 +34182,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -35149,7 +35149,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -36116,7 +36116,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -37231,7 +37231,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
@@ -38198,7 +38198,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -39313,7 +39313,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -40280,7 +40280,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">

--- a/diseases/d006/2010-2014.xlsx
+++ b/diseases/d006/2010-2014.xlsx
@@ -987,7 +987,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5112,7 +5112,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -5862,7 +5862,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -6987,7 +6987,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8112,7 +8112,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -8862,7 +8862,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -9612,7 +9612,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -9987,7 +9987,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -10737,7 +10737,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11112,7 +11112,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -11862,7 +11862,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12612,7 +12612,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -12987,7 +12987,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13806,7 +13806,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -14773,7 +14773,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15888,7 +15888,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -16855,7 +16855,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -17822,7 +17822,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -18789,7 +18789,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -19904,7 +19904,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -20871,7 +20871,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -21986,7 +21986,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -22953,7 +22953,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -23920,7 +23920,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -25035,7 +25035,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -26002,7 +26002,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -26969,7 +26969,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -29051,7 +29051,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -30166,7 +30166,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -31133,7 +31133,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -32100,7 +32100,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK186" t="inlineStr">
@@ -33067,7 +33067,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK192" t="inlineStr">
@@ -34182,7 +34182,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -35149,7 +35149,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -36116,7 +36116,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -37231,7 +37231,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
@@ -38198,7 +38198,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -39313,7 +39313,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -40280,7 +40280,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">

--- a/diseases/d006/2010-2014.xlsx
+++ b/diseases/d006/2010-2014.xlsx
@@ -987,7 +987,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5112,7 +5112,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -5862,7 +5862,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -6987,7 +6987,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8112,7 +8112,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -8862,7 +8862,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -9612,7 +9612,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -9987,7 +9987,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -10737,7 +10737,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11112,7 +11112,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -11862,7 +11862,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12612,7 +12612,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -12987,7 +12987,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13806,7 +13806,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -14773,7 +14773,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15888,7 +15888,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -16855,7 +16855,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -17822,7 +17822,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -18789,7 +18789,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -19904,7 +19904,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -20871,7 +20871,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -21986,7 +21986,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -22953,7 +22953,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -23920,7 +23920,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -25035,7 +25035,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -26002,7 +26002,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -26969,7 +26969,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -29051,7 +29051,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -30166,7 +30166,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -31133,7 +31133,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -32100,7 +32100,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK186" t="inlineStr">
@@ -33067,7 +33067,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK192" t="inlineStr">
@@ -34182,7 +34182,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -35149,7 +35149,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -36116,7 +36116,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -37231,7 +37231,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
@@ -38198,7 +38198,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -39313,7 +39313,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -40280,7 +40280,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
